--- a/data_analysis/data/R_output/Filamentoviridae_EVEs.xlsx
+++ b/data_analysis/data/R_output/Filamentoviridae_EVEs.xlsx
@@ -351,93 +351,173 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:AG42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LbFVorf5</t>
+          <t>YP_009345698.1</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>LbFVorf10</t>
+          <t>WKA13617.1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>LbFVorf38(lef-5)</t>
+          <t>YP_009345609.1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>LbFVorf60(lcat)</t>
+          <t>YP_009345689.1</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>LbFVorf68(helicase2)</t>
+          <t>YP_009345696.1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>LbFVorf72</t>
+          <t>YP_009345621.1</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>LbFVorf78(lef-9)</t>
+          <t>YP_009345700.1</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LbFVorf83</t>
+          <t>YP_009345672.1</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>LbFVorf85(Ac81)</t>
+          <t>YP_009345687.1</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>LbFVorf87</t>
+          <t>YP_009345682.1</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>LbFVorf92</t>
+          <t>YP_009345637.1</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>LbFVorf94</t>
+          <t>YP_009345706.1</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>LbFVorf96(lef-8)</t>
+          <t>YP_009345676.1</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>LbFVorf107(lef-4)</t>
+          <t>WKT15237.1</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>LbFVorf108</t>
+          <t>YP_009345664.1</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>LbFVDNApol</t>
+          <t>WKA13539.1</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>LbFVJmJC1</t>
+          <t>YP_009345711.1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>YP_009345662.1</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>YP_009345617.1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>WKT15245.1</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>YP_009345641.1</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>YP_009345685.1</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>YP_009345623.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>YP_009345710.1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>YP_009345656.1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>YP_009345606.1</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>WNK26554.1</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>YP_009345624.1</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>YP_009345667.1</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>WNK26569.1</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>YP_009345615.1</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>YP_009345691.1</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>YP_009345614.1</t>
         </is>
       </c>
     </row>
@@ -493,6 +573,54 @@
       <c r="Q2">
         <v>0</v>
       </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -546,6 +674,54 @@
       <c r="Q3">
         <v>0</v>
       </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -597,7 +773,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>1</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -652,6 +876,54 @@
       <c r="Q5">
         <v>0</v>
       </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -661,16 +933,16 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -679,42 +951,90 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="K6">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -738,25 +1058,73 @@
         <v>1</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7">
         <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -791,7 +1159,7 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -809,6 +1177,54 @@
         <v>0</v>
       </c>
       <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
         <v>0</v>
       </c>
     </row>
@@ -817,19 +1233,19 @@
         <v>1</v>
       </c>
       <c r="B9">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -838,30 +1254,78 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9">
         <v>1</v>
       </c>
       <c r="N9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
         <v>0</v>
       </c>
     </row>
@@ -873,7 +1337,7 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -882,10 +1346,10 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -894,48 +1358,96 @@
         <v>1</v>
       </c>
       <c r="J10">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="N10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P10">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>1</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -944,30 +1456,78 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11">
         <v>1</v>
       </c>
       <c r="N11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
         <v>0</v>
       </c>
     </row>
@@ -976,10 +1536,10 @@
         <v>1</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -988,7 +1548,7 @@
         <v>1</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1003,24 +1563,72 @@
         <v>1</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12">
         <v>1</v>
       </c>
       <c r="N12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>1</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
         <v>1</v>
       </c>
     </row>
@@ -1032,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="C13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1053,27 +1661,75 @@
         <v>1</v>
       </c>
       <c r="J13">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P13">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>1</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
         <v>0</v>
       </c>
     </row>
@@ -1129,58 +1785,154 @@
       <c r="Q14">
         <v>0</v>
       </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
       <c r="K15">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L15">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="N15">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>0.7</v>
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>1</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1191,10 +1943,10 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -1206,34 +1958,82 @@
         <v>1</v>
       </c>
       <c r="H16">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16">
         <v>1</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>1</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>1</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1268,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -1286,6 +2086,54 @@
         <v>0</v>
       </c>
       <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
         <v>0</v>
       </c>
     </row>
@@ -1309,16 +2157,16 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -1339,6 +2187,54 @@
         <v>0</v>
       </c>
       <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
         <v>0</v>
       </c>
     </row>
@@ -1374,7 +2270,7 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -1392,6 +2288,54 @@
         <v>0</v>
       </c>
       <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
         <v>0</v>
       </c>
     </row>
@@ -1415,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -1424,13 +2368,13 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -1445,6 +2389,54 @@
         <v>0</v>
       </c>
       <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>1</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
         <v>0</v>
       </c>
     </row>
@@ -1500,6 +2492,54 @@
       <c r="Q21">
         <v>0</v>
       </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -1553,6 +2593,54 @@
       <c r="Q22">
         <v>0</v>
       </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -1606,6 +2694,54 @@
       <c r="Q23">
         <v>0</v>
       </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -1657,7 +2793,55 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>1</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1710,7 +2894,55 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>1</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1765,6 +2997,54 @@
       <c r="Q26">
         <v>0</v>
       </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -1818,6 +3098,54 @@
       <c r="Q27">
         <v>0</v>
       </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -1860,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -1869,6 +3197,54 @@
         <v>0</v>
       </c>
       <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>1</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
         <v>0</v>
       </c>
     </row>
@@ -1924,6 +3300,54 @@
       <c r="Q29">
         <v>0</v>
       </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -1977,6 +3401,54 @@
       <c r="Q30">
         <v>0</v>
       </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -2030,6 +3502,54 @@
       <c r="Q31">
         <v>0</v>
       </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -2083,6 +3603,54 @@
       <c r="Q32">
         <v>0</v>
       </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -2136,6 +3704,54 @@
       <c r="Q33">
         <v>0</v>
       </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -2189,6 +3805,54 @@
       <c r="Q34">
         <v>0</v>
       </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -2204,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -2213,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2240,6 +3904,54 @@
         <v>0</v>
       </c>
       <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>1</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+      <c r="AG35">
         <v>0</v>
       </c>
     </row>
@@ -2295,6 +4007,54 @@
       <c r="Q36">
         <v>0</v>
       </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -2348,6 +4108,54 @@
       <c r="Q37">
         <v>0</v>
       </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -2401,6 +4209,54 @@
       <c r="Q38">
         <v>0</v>
       </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -2454,6 +4310,54 @@
       <c r="Q39">
         <v>0</v>
       </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>0</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>0</v>
+      </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -2507,19 +4411,67 @@
       <c r="Q40">
         <v>0</v>
       </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>0</v>
+      </c>
+      <c r="AD40">
+        <v>0</v>
+      </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
+        <v>0</v>
+      </c>
+      <c r="AG40">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
         <v>0</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2552,12 +4504,60 @@
         <v>0</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41">
+        <v>1</v>
+      </c>
+      <c r="AC41">
+        <v>0</v>
+      </c>
+      <c r="AD41">
+        <v>0</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>0</v>
+      </c>
+      <c r="AG41">
         <v>0</v>
       </c>
     </row>
@@ -2611,6 +4611,54 @@
         <v>0</v>
       </c>
       <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42">
+        <v>0</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>0</v>
+      </c>
+      <c r="AG42">
         <v>0</v>
       </c>
     </row>
